--- a/tables/datas/common/TbTerrainConfig.xlsx
+++ b/tables/datas/common/TbTerrainConfig.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,6 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -931,7 +930,6 @@
       <c r="T6" t="n">
         <v>0.3</v>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -999,7 +997,6 @@
       <c r="T7" t="n">
         <v>0.2</v>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -1067,7 +1064,6 @@
       <c r="T8" t="n">
         <v>0.2</v>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1135,7 +1131,6 @@
       <c r="T9" t="n">
         <v>0.3</v>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -1203,7 +1198,6 @@
       <c r="T10" t="n">
         <v>0.25</v>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -1271,7 +1265,6 @@
       <c r="T11" t="n">
         <v>0.35</v>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -1339,7 +1332,6 @@
       <c r="T12" t="n">
         <v>0.4</v>
       </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -1407,7 +1399,140 @@
       <c r="T13" t="n">
         <v>0.2</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>地形墙</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>不可行走的实体墙</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>38</v>
+      </c>
+      <c r="R14" t="n">
+        <v>38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>空气墙</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>不可行走的隐形屏障</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
